--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.67920557524901</v>
+        <v>6.447870905977965</v>
       </c>
       <c r="D2" t="n">
-        <v>39.4762951433926</v>
+        <v>6.414897960801299</v>
       </c>
       <c r="E2" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F2" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.19055767143413</v>
+        <v>7.018465621608046</v>
       </c>
       <c r="D3" t="n">
-        <v>43.00736544439674</v>
+        <v>6.988696884714471</v>
       </c>
       <c r="E3" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F3" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.06454324064481</v>
+        <v>5.697988276604781</v>
       </c>
       <c r="D4" t="n">
-        <v>34.9171434492245</v>
+        <v>5.674035810498983</v>
       </c>
       <c r="E4" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F4" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.08588270502318</v>
+        <v>4.238955939566266</v>
       </c>
       <c r="D5" t="n">
-        <v>25.92150284784447</v>
+        <v>4.212244212774727</v>
       </c>
       <c r="E5" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F5" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.80183061049915</v>
+        <v>2.730297474206112</v>
       </c>
       <c r="D6" t="n">
-        <v>16.59318812610012</v>
+        <v>2.69639307049127</v>
       </c>
       <c r="E6" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F6" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.98933683893576</v>
+        <v>3.735767236327061</v>
       </c>
       <c r="D7" t="n">
-        <v>22.86793331277414</v>
+        <v>3.716039163325798</v>
       </c>
       <c r="E7" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F7" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.45557888018645</v>
+        <v>5.111531568030299</v>
       </c>
       <c r="D8" t="n">
-        <v>31.36426204355732</v>
+        <v>5.096692582078066</v>
       </c>
       <c r="E8" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F8" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.19781527824757</v>
+        <v>6.36964498271523</v>
       </c>
       <c r="D9" t="n">
-        <v>39.13686300299901</v>
+        <v>6.359740237987339</v>
       </c>
       <c r="E9" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F9" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.34970727659704</v>
+        <v>1.194327432447019</v>
       </c>
       <c r="D10" t="n">
-        <v>7.234442980686314</v>
+        <v>1.175596984361526</v>
       </c>
       <c r="E10" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F10" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.82494185230635</v>
+        <v>2.246553050999783</v>
       </c>
       <c r="D11" t="n">
-        <v>14.01684680032165</v>
+        <v>2.277737605052268</v>
       </c>
       <c r="E11" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F11" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.44310275048061</v>
+        <v>4.622004196953099</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63712006638716</v>
+        <v>4.653532010787913</v>
       </c>
       <c r="E12" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F12" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.47889634394884</v>
+        <v>4.627820655891686</v>
       </c>
       <c r="D13" t="n">
-        <v>27.45657609755625</v>
+        <v>4.461693615852892</v>
       </c>
       <c r="E13" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F13" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.83494917406284</v>
+        <v>4.360679240785211</v>
       </c>
       <c r="D14" t="n">
-        <v>25.65283560347345</v>
+        <v>4.168585785564435</v>
       </c>
       <c r="E14" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F14" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.69415258733741</v>
+        <v>5.962799795442328</v>
       </c>
       <c r="D15" t="n">
-        <v>35.40887252201414</v>
+        <v>5.753941784827298</v>
       </c>
       <c r="E15" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F15" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>20.30746923152113</v>
+        <v>3.299963750122183</v>
       </c>
       <c r="D16" t="n">
-        <v>19.3381017104363</v>
+        <v>3.142441527945899</v>
       </c>
       <c r="E16" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F16" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>4.057193795050859</v>
+        <v>0.6592939916957645</v>
       </c>
       <c r="D17" t="n">
-        <v>2.851297263923607</v>
+        <v>0.4633358053875862</v>
       </c>
       <c r="E17" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F17" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.59262274275288</v>
+        <v>3.021301195697344</v>
       </c>
       <c r="D18" t="n">
-        <v>20.03028684144764</v>
+        <v>3.254921611735242</v>
       </c>
       <c r="E18" t="n">
-        <v>10.99174750789975</v>
+        <v>1.786158970033709</v>
       </c>
       <c r="F18" t="n">
-        <v>10.99606978466091</v>
+        <v>1.786861340007398</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
